--- a/output/Test_Cases_collection/TC10 - Logout from Inventory Page.xlsx
+++ b/output/Test_Cases_collection/TC10 - Logout from Inventory Page.xlsx
@@ -76,22 +76,22 @@
     <t>Click on "logout_sidebar_link"</t>
   </si>
   <si>
-    <t>The login page is displayed.</t>
-  </si>
-  <si>
-    <t>Username is entered successfully.</t>
-  </si>
-  <si>
-    <t>Password is entered successfully.</t>
-  </si>
-  <si>
-    <t>User is redirected to [https://www.saucedemo.com/inventory.html].</t>
-  </si>
-  <si>
-    <t>Sidebar menu is displayed.</t>
-  </si>
-  <si>
-    <t>User is redirected to [https://www.saucedemo.com/].</t>
+    <t>The application login page is displayed.</t>
+  </si>
+  <si>
+    <t>The username is entered successfully.</t>
+  </si>
+  <si>
+    <t>The password is entered successfully.</t>
+  </si>
+  <si>
+    <t>The user is redirected to the inventory page.</t>
+  </si>
+  <si>
+    <t>The sidebar menu is displayed.</t>
+  </si>
+  <si>
+    <t>The user is logged out and redirected to the login page.</t>
   </si>
   <si>
     <t>New</t>
